--- a/05_Figures/F05_classification/MANIFEST.xlsx
+++ b/05_Figures/F05_classification/MANIFEST.xlsx
@@ -1687,9 +1687,15 @@
       <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="J2"/>
-      <c r="K2"/>
-      <c r="L2"/>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0694642857142857</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.199209335364792</v>
+      </c>
       <c r="M2" t="b">
         <v>0</v>
       </c>
@@ -1740,9 +1746,15 @@
       <c r="I3" t="n">
         <v>0</v>
       </c>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0728571428571428</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.216483110032967</v>
+      </c>
       <c r="M3" t="b">
         <v>0</v>
       </c>
@@ -1793,9 +1805,15 @@
       <c r="I4" t="n">
         <v>0.196428571428571</v>
       </c>
-      <c r="J4"/>
-      <c r="K4"/>
-      <c r="L4"/>
+      <c r="J4" t="n">
+        <v>0.263681592039801</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.138035714285714</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.181664790036149</v>
+      </c>
       <c r="M4" t="b">
         <v>0</v>
       </c>
@@ -1846,9 +1864,15 @@
       <c r="I5" t="n">
         <v>0.455357142857143</v>
       </c>
-      <c r="J5"/>
-      <c r="K5"/>
-      <c r="L5"/>
+      <c r="J5" t="n">
+        <v>0.606965174129353</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.5065625</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.197424296848772</v>
+      </c>
       <c r="M5" t="b">
         <v>0</v>
       </c>
@@ -1899,9 +1923,15 @@
       <c r="I6" t="n">
         <v>0.5</v>
       </c>
-      <c r="J6"/>
-      <c r="K6"/>
-      <c r="L6"/>
+      <c r="J6" t="n">
+        <v>0.298507462686567</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.368303571428571</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.203488112035621</v>
+      </c>
       <c r="M6" t="b">
         <v>0</v>
       </c>
@@ -1952,9 +1982,15 @@
       <c r="I7" t="n">
         <v>0</v>
       </c>
-      <c r="J7"/>
-      <c r="K7"/>
-      <c r="L7"/>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0238392857142857</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.112187953893319</v>
+      </c>
       <c r="M7" t="b">
         <v>0</v>
       </c>
@@ -2005,9 +2041,15 @@
       <c r="I8" t="n">
         <v>0.5</v>
       </c>
-      <c r="J8"/>
-      <c r="K8"/>
-      <c r="L8"/>
+      <c r="J8" t="n">
+        <v>0.373134328358209</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.410089285714286</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.213726968807571</v>
+      </c>
       <c r="M8" t="b">
         <v>0</v>
       </c>
@@ -2053,14 +2095,20 @@
         <v>23</v>
       </c>
       <c r="H9" t="n">
-        <v>0.482142857142857</v>
+        <v>0.339285714285714</v>
       </c>
       <c r="I9" t="n">
-        <v>0.482142857142857</v>
-      </c>
-      <c r="J9"/>
-      <c r="K9"/>
-      <c r="L9"/>
+        <v>0.339285714285714</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.393034825870647</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.305982142857143</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.251078827400813</v>
+      </c>
       <c r="M9" t="b">
         <v>0</v>
       </c>
@@ -2111,9 +2159,15 @@
       <c r="I10" t="n">
         <v>0</v>
       </c>
-      <c r="J10"/>
-      <c r="K10"/>
-      <c r="L10"/>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0658928571428571</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.186553391087878</v>
+      </c>
       <c r="M10" t="b">
         <v>0</v>
       </c>
@@ -2164,9 +2218,15 @@
       <c r="I11" t="n">
         <v>0</v>
       </c>
-      <c r="J11"/>
-      <c r="K11"/>
-      <c r="L11"/>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0757142857142857</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.206053277165054</v>
+      </c>
       <c r="M11" t="b">
         <v>0</v>
       </c>
@@ -2217,9 +2277,15 @@
       <c r="I12" t="n">
         <v>0</v>
       </c>
-      <c r="J12"/>
-      <c r="K12"/>
-      <c r="L12"/>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.194464285714286</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.234766839494559</v>
+      </c>
       <c r="M12" t="b">
         <v>0</v>
       </c>
@@ -2270,9 +2336,15 @@
       <c r="I13" t="n">
         <v>0.732142857142857</v>
       </c>
-      <c r="J13"/>
-      <c r="K13"/>
-      <c r="L13"/>
+      <c r="J13" t="n">
+        <v>0.139303482587065</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.518883928571429</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.180024101817027</v>
+      </c>
       <c r="M13" t="b">
         <v>0</v>
       </c>
@@ -2323,9 +2395,15 @@
       <c r="I14" t="n">
         <v>0.285714285714286</v>
       </c>
-      <c r="J14"/>
-      <c r="K14"/>
-      <c r="L14"/>
+      <c r="J14" t="n">
+        <v>0.641791044776119</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.383303571428571</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.219697730525772</v>
+      </c>
       <c r="M14" t="b">
         <v>0</v>
       </c>
@@ -2376,9 +2454,15 @@
       <c r="I15" t="n">
         <v>0</v>
       </c>
-      <c r="J15"/>
-      <c r="K15"/>
-      <c r="L15"/>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.15793582152458</v>
+      </c>
       <c r="M15" t="b">
         <v>0</v>
       </c>
@@ -2429,9 +2513,15 @@
       <c r="I16" t="n">
         <v>0.303571428571429</v>
       </c>
-      <c r="J16"/>
-      <c r="K16"/>
-      <c r="L16"/>
+      <c r="J16" t="n">
+        <v>0.751243781094527</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.44125</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.223011142306527</v>
+      </c>
       <c r="M16" t="b">
         <v>0</v>
       </c>
@@ -2477,14 +2567,20 @@
         <v>23</v>
       </c>
       <c r="H17" t="n">
-        <v>0.125</v>
+        <v>0.160714285714286</v>
       </c>
       <c r="I17" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="J17"/>
-      <c r="K17"/>
-      <c r="L17"/>
+        <v>0.160714285714286</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.601990049751244</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.296428571428571</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.259991598359084</v>
+      </c>
       <c r="M17" t="b">
         <v>0</v>
       </c>
@@ -2535,9 +2631,15 @@
       <c r="I18" t="n">
         <v>0</v>
       </c>
-      <c r="J18"/>
-      <c r="K18"/>
-      <c r="L18"/>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.0630357142857143</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.184180656849469</v>
+      </c>
       <c r="M18" t="b">
         <v>0</v>
       </c>
@@ -2588,9 +2690,15 @@
       <c r="I19" t="n">
         <v>0</v>
       </c>
-      <c r="J19"/>
-      <c r="K19"/>
-      <c r="L19"/>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.0573214285714286</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.172153047837694</v>
+      </c>
       <c r="M19" t="b">
         <v>0</v>
       </c>
@@ -2641,9 +2749,15 @@
       <c r="I20" t="n">
         <v>0</v>
       </c>
-      <c r="J20"/>
-      <c r="K20"/>
-      <c r="L20"/>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.153125</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.205860306981865</v>
+      </c>
       <c r="M20" t="b">
         <v>0</v>
       </c>
@@ -2694,9 +2808,15 @@
       <c r="I21" t="n">
         <v>0.321428571428571</v>
       </c>
-      <c r="J21"/>
-      <c r="K21"/>
-      <c r="L21"/>
+      <c r="J21" t="n">
+        <v>0.880597014925373</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.507276785714286</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.184520600647326</v>
+      </c>
       <c r="M21" t="b">
         <v>0</v>
       </c>
@@ -2747,9 +2867,15 @@
       <c r="I22" t="n">
         <v>0.339285714285714</v>
       </c>
-      <c r="J22"/>
-      <c r="K22"/>
-      <c r="L22"/>
+      <c r="J22" t="n">
+        <v>0.582089552238806</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.369196428571429</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.22997522904937</v>
+      </c>
       <c r="M22" t="b">
         <v>0</v>
       </c>
@@ -2800,9 +2926,15 @@
       <c r="I23" t="n">
         <v>0</v>
       </c>
-      <c r="J23"/>
-      <c r="K23"/>
-      <c r="L23"/>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.0284821428571429</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.131455663300222</v>
+      </c>
       <c r="M23" t="b">
         <v>0</v>
       </c>
@@ -2853,9 +2985,15 @@
       <c r="I24" t="n">
         <v>0.321428571428571</v>
       </c>
-      <c r="J24"/>
-      <c r="K24"/>
-      <c r="L24"/>
+      <c r="J24" t="n">
+        <v>0.686567164179104</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.422053571428571</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.212228228880443</v>
+      </c>
       <c r="M24" t="b">
         <v>0</v>
       </c>
@@ -2901,14 +3039,20 @@
         <v>23</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0892857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0892857142857143</v>
-      </c>
-      <c r="J25"/>
-      <c r="K25"/>
-      <c r="L25"/>
+        <v>0.0714285714285714</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.825870646766169</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.306339285714286</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.237523899854849</v>
+      </c>
       <c r="M25" t="b">
         <v>0</v>
       </c>
@@ -2959,9 +3103,15 @@
       <c r="I26" t="n">
         <v>0</v>
       </c>
-      <c r="J26"/>
-      <c r="K26"/>
-      <c r="L26"/>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.0603571428571428</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.181945510533236</v>
+      </c>
       <c r="M26" t="b">
         <v>0</v>
       </c>
@@ -3012,9 +3162,15 @@
       <c r="I27" t="n">
         <v>0</v>
       </c>
-      <c r="J27"/>
-      <c r="K27"/>
-      <c r="L27"/>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.0603571428571428</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.189401994651296</v>
+      </c>
       <c r="M27" t="b">
         <v>0</v>
       </c>
@@ -3065,9 +3221,15 @@
       <c r="I28" t="n">
         <v>0.0892857142857143</v>
       </c>
-      <c r="J28"/>
-      <c r="K28"/>
-      <c r="L28"/>
+      <c r="J28" t="n">
+        <v>0.412935323383085</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.125535714285714</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.189768394725123</v>
+      </c>
       <c r="M28" t="b">
         <v>0</v>
       </c>
@@ -3118,9 +3280,15 @@
       <c r="I29" t="n">
         <v>0.383928571428571</v>
       </c>
-      <c r="J29"/>
-      <c r="K29"/>
-      <c r="L29"/>
+      <c r="J29" t="n">
+        <v>0.761194029850746</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.509732142857143</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.183228902390461</v>
+      </c>
       <c r="M29" t="b">
         <v>0</v>
       </c>
@@ -3171,9 +3339,15 @@
       <c r="I30" t="n">
         <v>0.321428571428571</v>
       </c>
-      <c r="J30"/>
-      <c r="K30"/>
-      <c r="L30"/>
+      <c r="J30" t="n">
+        <v>0.512437810945274</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.343035714285714</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.211550729513821</v>
+      </c>
       <c r="M30" t="b">
         <v>0</v>
       </c>
@@ -3224,9 +3398,15 @@
       <c r="I31" t="n">
         <v>0</v>
       </c>
-      <c r="J31"/>
-      <c r="K31"/>
-      <c r="L31"/>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.0297321428571428</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.137487442439411</v>
+      </c>
       <c r="M31" t="b">
         <v>0</v>
       </c>
@@ -3277,9 +3457,15 @@
       <c r="I32" t="n">
         <v>0.446428571428571</v>
       </c>
-      <c r="J32"/>
-      <c r="K32"/>
-      <c r="L32"/>
+      <c r="J32" t="n">
+        <v>0.3681592039801</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.377767857142857</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.226416177411875</v>
+      </c>
       <c r="M32" t="b">
         <v>0</v>
       </c>
@@ -3325,14 +3511,20 @@
         <v>23</v>
       </c>
       <c r="H33" t="n">
-        <v>0.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0.142857142857143</v>
-      </c>
-      <c r="J33"/>
-      <c r="K33"/>
-      <c r="L33"/>
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.280446428571429</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.247635194608436</v>
+      </c>
       <c r="M33" t="b">
         <v>0</v>
       </c>
@@ -3383,9 +3575,15 @@
       <c r="I34" t="n">
         <v>0</v>
       </c>
-      <c r="J34"/>
-      <c r="K34"/>
-      <c r="L34"/>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.0451041666666667</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.155394819138373</v>
+      </c>
       <c r="M34" t="b">
         <v>0</v>
       </c>
@@ -3436,9 +3634,15 @@
       <c r="I35" t="n">
         <v>0</v>
       </c>
-      <c r="J35"/>
-      <c r="K35"/>
-      <c r="L35"/>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.0451041666666667</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.159098168969622</v>
+      </c>
       <c r="M35" t="b">
         <v>0</v>
       </c>
@@ -3489,9 +3693,15 @@
       <c r="I36" t="n">
         <v>0</v>
       </c>
-      <c r="J36"/>
-      <c r="K36"/>
-      <c r="L36"/>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.104895833333333</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.180384208601723</v>
+      </c>
       <c r="M36" t="b">
         <v>0</v>
       </c>
@@ -3542,9 +3752,15 @@
       <c r="I37" t="n">
         <v>0.354166666666667</v>
       </c>
-      <c r="J37"/>
-      <c r="K37"/>
-      <c r="L37"/>
+      <c r="J37" t="n">
+        <v>0.890547263681592</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.562604166666667</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.248828192280237</v>
+      </c>
       <c r="M37" t="b">
         <v>0</v>
       </c>
@@ -3595,9 +3811,15 @@
       <c r="I38" t="n">
         <v>0.4375</v>
       </c>
-      <c r="J38"/>
-      <c r="K38"/>
-      <c r="L38"/>
+      <c r="J38" t="n">
+        <v>0.278606965174129</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.319479166666667</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.20154646107937</v>
+      </c>
       <c r="M38" t="b">
         <v>0</v>
       </c>
@@ -3648,9 +3870,15 @@
       <c r="I39" t="n">
         <v>0</v>
       </c>
-      <c r="J39"/>
-      <c r="K39"/>
-      <c r="L39"/>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.0276041666666667</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.131512003852555</v>
+      </c>
       <c r="M39" t="b">
         <v>0</v>
       </c>
@@ -3701,9 +3929,15 @@
       <c r="I40" t="n">
         <v>0.270833333333333</v>
       </c>
-      <c r="J40"/>
-      <c r="K40"/>
-      <c r="L40"/>
+      <c r="J40" t="n">
+        <v>0.701492537313433</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.384479166666667</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.218828976929277</v>
+      </c>
       <c r="M40" t="b">
         <v>0</v>
       </c>
@@ -3749,14 +3983,20 @@
         <v>23</v>
       </c>
       <c r="H41" t="n">
-        <v>0.25</v>
+        <v>0.375</v>
       </c>
       <c r="I41" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J41"/>
-      <c r="K41"/>
-      <c r="L41"/>
+        <v>0.375</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.343283582089552</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.296770833333333</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.25374513246453</v>
+      </c>
       <c r="M41" t="b">
         <v>0</v>
       </c>
@@ -3807,9 +4047,15 @@
       <c r="I42" t="n">
         <v>0</v>
       </c>
-      <c r="J42"/>
-      <c r="K42"/>
-      <c r="L42"/>
+      <c r="J42" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.0759374999999999</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.197883851859551</v>
+      </c>
       <c r="M42" t="b">
         <v>0</v>
       </c>
@@ -3860,9 +4106,15 @@
       <c r="I43" t="n">
         <v>0</v>
       </c>
-      <c r="J43"/>
-      <c r="K43"/>
-      <c r="L43"/>
+      <c r="J43" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.0841666666666667</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.210694740962718</v>
+      </c>
       <c r="M43" t="b">
         <v>0</v>
       </c>
@@ -3913,9 +4165,15 @@
       <c r="I44" t="n">
         <v>0</v>
       </c>
-      <c r="J44"/>
-      <c r="K44"/>
-      <c r="L44"/>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.142395833333333</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.221119144989096</v>
+      </c>
       <c r="M44" t="b">
         <v>0</v>
       </c>
@@ -3966,9 +4224,15 @@
       <c r="I45" t="n">
         <v>0.645833333333333</v>
       </c>
-      <c r="J45"/>
-      <c r="K45"/>
-      <c r="L45"/>
+      <c r="J45" t="n">
+        <v>0.26865671641791</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.511770833333333</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.19818044773011</v>
+      </c>
       <c r="M45" t="b">
         <v>0</v>
       </c>
@@ -4019,9 +4283,15 @@
       <c r="I46" t="n">
         <v>0.104166666666667</v>
       </c>
-      <c r="J46"/>
-      <c r="K46"/>
-      <c r="L46"/>
+      <c r="J46" t="n">
+        <v>0.850746268656716</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.343333333333333</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.21735050247666</v>
+      </c>
       <c r="M46" t="b">
         <v>0</v>
       </c>
@@ -4072,9 +4342,15 @@
       <c r="I47" t="n">
         <v>0</v>
       </c>
-      <c r="J47"/>
-      <c r="K47"/>
-      <c r="L47"/>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.0298958333333334</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.14050255619149</v>
+      </c>
       <c r="M47" t="b">
         <v>0</v>
       </c>
@@ -4125,9 +4401,15 @@
       <c r="I48" t="n">
         <v>0.229166666666667</v>
       </c>
-      <c r="J48"/>
-      <c r="K48"/>
-      <c r="L48"/>
+      <c r="J48" t="n">
+        <v>0.761194029850746</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.417604166666667</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.22714769902877</v>
+      </c>
       <c r="M48" t="b">
         <v>0</v>
       </c>
@@ -4173,14 +4455,20 @@
         <v>23</v>
       </c>
       <c r="H49" t="n">
-        <v>0.104166666666667</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="I49" t="n">
-        <v>0.104166666666667</v>
-      </c>
-      <c r="J49"/>
-      <c r="K49"/>
-      <c r="L49"/>
+        <v>0.166666666666667</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.611940298507463</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.296770833333333</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.25582529133498</v>
+      </c>
       <c r="M49" t="b">
         <v>0</v>
       </c>
@@ -4231,9 +4519,15 @@
       <c r="I50" t="n">
         <v>0</v>
       </c>
-      <c r="J50"/>
-      <c r="K50"/>
-      <c r="L50"/>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.0741666666666666</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.199636744373565</v>
+      </c>
       <c r="M50" t="b">
         <v>0</v>
       </c>
@@ -4284,9 +4578,15 @@
       <c r="I51" t="n">
         <v>0</v>
       </c>
-      <c r="J51"/>
-      <c r="K51"/>
-      <c r="L51"/>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.0742708333333334</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.197505220080637</v>
+      </c>
       <c r="M51" t="b">
         <v>0</v>
       </c>
@@ -4337,9 +4637,15 @@
       <c r="I52" t="n">
         <v>0</v>
       </c>
-      <c r="J52"/>
-      <c r="K52"/>
-      <c r="L52"/>
+      <c r="J52" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.183125</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.23398029998035</v>
+      </c>
       <c r="M52" t="b">
         <v>0</v>
       </c>
@@ -4390,9 +4696,15 @@
       <c r="I53" t="n">
         <v>0.1875</v>
       </c>
-      <c r="J53"/>
-      <c r="K53"/>
-      <c r="L53"/>
+      <c r="J53" t="n">
+        <v>0.706467661691542</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.335625</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.216635156676656</v>
+      </c>
       <c r="M53" t="b">
         <v>0</v>
       </c>
@@ -4443,9 +4755,15 @@
       <c r="I54" t="n">
         <v>0</v>
       </c>
-      <c r="J54"/>
-      <c r="K54"/>
-      <c r="L54"/>
+      <c r="J54" t="n">
+        <v>1</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.0040625</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.0337867959661506</v>
+      </c>
       <c r="M54" t="b">
         <v>0</v>
       </c>
@@ -4496,9 +4814,15 @@
       <c r="I55" t="n">
         <v>0.333333333333333</v>
       </c>
-      <c r="J55"/>
-      <c r="K55"/>
-      <c r="L55"/>
+      <c r="J55" t="n">
+        <v>0.651741293532338</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.425520833333333</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.221441057805316</v>
+      </c>
       <c r="M55" t="b">
         <v>0</v>
       </c>
@@ -4544,14 +4868,20 @@
         <v>23</v>
       </c>
       <c r="H56" t="n">
-        <v>0.104166666666667</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="I56" t="n">
-        <v>0.104166666666667</v>
-      </c>
-      <c r="J56"/>
-      <c r="K56"/>
-      <c r="L56"/>
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.890547263681592</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.335208333333333</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.257488266985894</v>
+      </c>
       <c r="M56" t="b">
         <v>0</v>
       </c>
@@ -4602,9 +4932,15 @@
       <c r="I57" t="n">
         <v>0.142857142857143</v>
       </c>
-      <c r="J57"/>
-      <c r="K57"/>
-      <c r="L57"/>
+      <c r="J57" t="n">
+        <v>0.199004975124378</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.105982142857143</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.225962638790841</v>
+      </c>
       <c r="M57" t="b">
         <v>0</v>
       </c>
@@ -4655,9 +4991,15 @@
       <c r="I58" t="n">
         <v>0.321428571428571</v>
       </c>
-      <c r="J58"/>
-      <c r="K58"/>
-      <c r="L58"/>
+      <c r="J58" t="n">
+        <v>0.169154228855721</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.116071428571429</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.252519099882679</v>
+      </c>
       <c r="M58" t="b">
         <v>0</v>
       </c>
@@ -4708,9 +5050,15 @@
       <c r="I59" t="n">
         <v>0.125</v>
       </c>
-      <c r="J59"/>
-      <c r="K59"/>
-      <c r="L59"/>
+      <c r="J59" t="n">
+        <v>0.572139303482587</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.213839285714286</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.221206421660859</v>
+      </c>
       <c r="M59" t="b">
         <v>0</v>
       </c>
@@ -4761,9 +5109,15 @@
       <c r="I60" t="n">
         <v>0.660714285714286</v>
       </c>
-      <c r="J60"/>
-      <c r="K60"/>
-      <c r="L60"/>
+      <c r="J60" t="n">
+        <v>0.0597014925373134</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0.319107142857143</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.20099924398478</v>
+      </c>
       <c r="M60" t="b">
         <v>0</v>
       </c>
@@ -4814,9 +5168,15 @@
       <c r="I61" t="n">
         <v>0</v>
       </c>
-      <c r="J61"/>
-      <c r="K61"/>
-      <c r="L61"/>
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.0158928571428571</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.090856428083261</v>
+      </c>
       <c r="M61" t="b">
         <v>0</v>
       </c>
@@ -4867,9 +5227,15 @@
       <c r="I62" t="n">
         <v>0.642857142857143</v>
       </c>
-      <c r="J62"/>
-      <c r="K62"/>
-      <c r="L62"/>
+      <c r="J62" t="n">
+        <v>0.203980099502488</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0.420982142857143</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.23962845173312</v>
+      </c>
       <c r="M62" t="b">
         <v>0</v>
       </c>
@@ -4920,9 +5286,15 @@
       <c r="I63" t="n">
         <v>0</v>
       </c>
-      <c r="J63"/>
-      <c r="K63"/>
-      <c r="L63"/>
+      <c r="J63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0.314642857142857</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.238489772425645</v>
+      </c>
       <c r="M63" t="b">
         <v>0</v>
       </c>
@@ -4973,9 +5345,15 @@
       <c r="I64" t="n">
         <v>0</v>
       </c>
-      <c r="J64"/>
-      <c r="K64"/>
-      <c r="L64"/>
+      <c r="J64" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0.0920535714285714</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.201435545610708</v>
+      </c>
       <c r="M64" t="b">
         <v>0</v>
       </c>
@@ -5026,9 +5404,15 @@
       <c r="I65" t="n">
         <v>0.375</v>
       </c>
-      <c r="J65"/>
-      <c r="K65"/>
-      <c r="L65"/>
+      <c r="J65" t="n">
+        <v>0.144278606965174</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0.100446428571429</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.219723694408278</v>
+      </c>
       <c r="M65" t="b">
         <v>0</v>
       </c>
@@ -5079,9 +5463,15 @@
       <c r="I66" t="n">
         <v>0</v>
       </c>
-      <c r="J66"/>
-      <c r="K66"/>
-      <c r="L66"/>
+      <c r="J66" t="n">
+        <v>1</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0.2375</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.239919578106015</v>
+      </c>
       <c r="M66" t="b">
         <v>0</v>
       </c>
@@ -5132,9 +5522,15 @@
       <c r="I67" t="n">
         <v>0.267857142857143</v>
       </c>
-      <c r="J67"/>
-      <c r="K67"/>
-      <c r="L67"/>
+      <c r="J67" t="n">
+        <v>0.621890547263682</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0.353303571428571</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.211105540824327</v>
+      </c>
       <c r="M67" t="b">
         <v>0</v>
       </c>
@@ -5185,9 +5581,15 @@
       <c r="I68" t="n">
         <v>0</v>
       </c>
-      <c r="J68"/>
-      <c r="K68"/>
-      <c r="L68"/>
+      <c r="J68" t="n">
+        <v>1</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0.0236607142857143</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.100201978811743</v>
+      </c>
       <c r="M68" t="b">
         <v>0</v>
       </c>
@@ -5238,9 +5640,15 @@
       <c r="I69" t="n">
         <v>0.678571428571428</v>
       </c>
-      <c r="J69"/>
-      <c r="K69"/>
-      <c r="L69"/>
+      <c r="J69" t="n">
+        <v>0.18407960199005</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0.449196428571429</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.219019979681869</v>
+      </c>
       <c r="M69" t="b">
         <v>0</v>
       </c>
@@ -5286,14 +5694,20 @@
         <v>23</v>
       </c>
       <c r="H70" t="n">
-        <v>0.5</v>
+        <v>0.446428571428571</v>
       </c>
       <c r="I70" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J70"/>
-      <c r="K70"/>
-      <c r="L70"/>
+        <v>0.446428571428571</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.348258706467662</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0.335535714285714</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.254413092607442</v>
+      </c>
       <c r="M70" t="b">
         <v>0</v>
       </c>
@@ -5344,9 +5758,15 @@
       <c r="I71" t="n">
         <v>0</v>
       </c>
-      <c r="J71"/>
-      <c r="K71"/>
-      <c r="L71"/>
+      <c r="J71" t="n">
+        <v>1</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0.105178571428571</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0.22170100821231</v>
+      </c>
       <c r="M71" t="b">
         <v>0</v>
       </c>
@@ -5397,9 +5817,15 @@
       <c r="I72" t="n">
         <v>0</v>
       </c>
-      <c r="J72"/>
-      <c r="K72"/>
-      <c r="L72"/>
+      <c r="J72" t="n">
+        <v>1</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0.107678571428571</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.229486779311536</v>
+      </c>
       <c r="M72" t="b">
         <v>0</v>
       </c>
@@ -5450,9 +5876,15 @@
       <c r="I73" t="n">
         <v>0.125</v>
       </c>
-      <c r="J73"/>
-      <c r="K73"/>
-      <c r="L73"/>
+      <c r="J73" t="n">
+        <v>0.572139303482587</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0.216696428571429</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.223664674832714</v>
+      </c>
       <c r="M73" t="b">
         <v>0</v>
       </c>
@@ -5503,9 +5935,15 @@
       <c r="I74" t="n">
         <v>0.178571428571429</v>
       </c>
-      <c r="J74"/>
-      <c r="K74"/>
-      <c r="L74"/>
+      <c r="J74" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0.308839285714286</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.21639750792289</v>
+      </c>
       <c r="M74" t="b">
         <v>0</v>
       </c>
@@ -5556,9 +5994,15 @@
       <c r="I75" t="n">
         <v>0</v>
       </c>
-      <c r="J75"/>
-      <c r="K75"/>
-      <c r="L75"/>
+      <c r="J75" t="n">
+        <v>1</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0.0158035714285714</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.0788535344606292</v>
+      </c>
       <c r="M75" t="b">
         <v>0</v>
       </c>
@@ -5609,9 +6053,15 @@
       <c r="I76" t="n">
         <v>0.214285714285714</v>
       </c>
-      <c r="J76"/>
-      <c r="K76"/>
-      <c r="L76"/>
+      <c r="J76" t="n">
+        <v>0.786069651741294</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0.416785714285714</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0.221293349629159</v>
+      </c>
       <c r="M76" t="b">
         <v>0</v>
       </c>
@@ -5657,14 +6107,20 @@
         <v>23</v>
       </c>
       <c r="H77" t="n">
-        <v>0.178571428571429</v>
+        <v>0.107142857142857</v>
       </c>
       <c r="I77" t="n">
-        <v>0.178571428571429</v>
-      </c>
-      <c r="J77"/>
-      <c r="K77"/>
-      <c r="L77"/>
+        <v>0.107142857142857</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.736318407960199</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0.343035714285714</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.258691533206804</v>
+      </c>
       <c r="M77" t="b">
         <v>0</v>
       </c>
@@ -5715,9 +6171,15 @@
       <c r="I78" t="n">
         <v>0.107142857142857</v>
       </c>
-      <c r="J78"/>
-      <c r="K78"/>
-      <c r="L78"/>
+      <c r="J78" t="n">
+        <v>0.194029850746269</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0.0734821428571429</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0.187134745766301</v>
+      </c>
       <c r="M78" t="b">
         <v>0</v>
       </c>
@@ -5768,9 +6230,15 @@
       <c r="I79" t="n">
         <v>0.125</v>
       </c>
-      <c r="J79"/>
-      <c r="K79"/>
-      <c r="L79"/>
+      <c r="J79" t="n">
+        <v>0.169154228855721</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0.0705357142857143</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.181964796908967</v>
+      </c>
       <c r="M79" t="b">
         <v>0</v>
       </c>
@@ -5821,9 +6289,15 @@
       <c r="I80" t="n">
         <v>0.25</v>
       </c>
-      <c r="J80"/>
-      <c r="K80"/>
-      <c r="L80"/>
+      <c r="J80" t="n">
+        <v>0.343283582089552</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0.206875</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0.242525410416037</v>
+      </c>
       <c r="M80" t="b">
         <v>0</v>
       </c>
@@ -5874,9 +6348,15 @@
       <c r="I81" t="n">
         <v>0.482142857142857</v>
       </c>
-      <c r="J81"/>
-      <c r="K81"/>
-      <c r="L81"/>
+      <c r="J81" t="n">
+        <v>0.263681592039801</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0.311160714285714</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.218179488468298</v>
+      </c>
       <c r="M81" t="b">
         <v>0</v>
       </c>
@@ -5927,9 +6407,15 @@
       <c r="I82" t="n">
         <v>0</v>
       </c>
-      <c r="J82"/>
-      <c r="K82"/>
-      <c r="L82"/>
+      <c r="J82" t="n">
+        <v>1</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0.0153571428571429</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0.0957217320393703</v>
+      </c>
       <c r="M82" t="b">
         <v>0</v>
       </c>
@@ -5980,9 +6466,15 @@
       <c r="I83" t="n">
         <v>0.678571428571429</v>
       </c>
-      <c r="J83"/>
-      <c r="K83"/>
-      <c r="L83"/>
+      <c r="J83" t="n">
+        <v>0.134328358208955</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0.403660714285714</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0.213505830614023</v>
+      </c>
       <c r="M83" t="b">
         <v>0</v>
       </c>
@@ -6028,14 +6520,20 @@
         <v>23</v>
       </c>
       <c r="H84" t="n">
-        <v>0.232142857142857</v>
+        <v>0.321428571428571</v>
       </c>
       <c r="I84" t="n">
-        <v>0.232142857142857</v>
-      </c>
-      <c r="J84"/>
-      <c r="K84"/>
-      <c r="L84"/>
+        <v>0.321428571428571</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.432835820895522</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0.314375</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0.25799254346659</v>
+      </c>
       <c r="M84" t="b">
         <v>0</v>
       </c>
@@ -6086,9 +6584,15 @@
       <c r="I85" t="n">
         <v>0</v>
       </c>
-      <c r="J85"/>
-      <c r="K85"/>
-      <c r="L85"/>
+      <c r="J85" t="n">
+        <v>1</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0.0682291666666667</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0.183994277183159</v>
+      </c>
       <c r="M85" t="b">
         <v>0</v>
       </c>
@@ -6139,9 +6643,15 @@
       <c r="I86" t="n">
         <v>0</v>
       </c>
-      <c r="J86"/>
-      <c r="K86"/>
-      <c r="L86"/>
+      <c r="J86" t="n">
+        <v>1</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0.0696875</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0.183182392514333</v>
+      </c>
       <c r="M86" t="b">
         <v>0</v>
       </c>
@@ -6192,9 +6702,15 @@
       <c r="I87" t="n">
         <v>0</v>
       </c>
-      <c r="J87"/>
-      <c r="K87"/>
-      <c r="L87"/>
+      <c r="J87" t="n">
+        <v>1</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0.157708333333333</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0.230712862909005</v>
+      </c>
       <c r="M87" t="b">
         <v>0</v>
       </c>
@@ -6245,9 +6761,15 @@
       <c r="I88" t="n">
         <v>0.416666666666667</v>
       </c>
-      <c r="J88"/>
-      <c r="K88"/>
-      <c r="L88"/>
+      <c r="J88" t="n">
+        <v>0.27363184079602</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0.293333333333333</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0.210513715864978</v>
+      </c>
       <c r="M88" t="b">
         <v>0</v>
       </c>
@@ -6298,9 +6820,15 @@
       <c r="I89" t="n">
         <v>0</v>
       </c>
-      <c r="J89"/>
-      <c r="K89"/>
-      <c r="L89"/>
+      <c r="J89" t="n">
+        <v>1</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0.0233333333333333</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.111274656299454</v>
+      </c>
       <c r="M89" t="b">
         <v>0</v>
       </c>
@@ -6351,9 +6879,15 @@
       <c r="I90" t="n">
         <v>0.291666666666667</v>
       </c>
-      <c r="J90"/>
-      <c r="K90"/>
-      <c r="L90"/>
+      <c r="J90" t="n">
+        <v>0.716417910447761</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0.419375</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0.225006106840632</v>
+      </c>
       <c r="M90" t="b">
         <v>0</v>
       </c>
@@ -6399,14 +6933,20 @@
         <v>23</v>
       </c>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>0.0833333333333333</v>
       </c>
       <c r="I91" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91"/>
-      <c r="K91"/>
-      <c r="L91"/>
+        <v>0.0833333333333333</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0.756218905472637</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0.3034375</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0.255987906608581</v>
+      </c>
       <c r="M91" t="b">
         <v>0</v>
       </c>
@@ -6457,9 +6997,15 @@
       <c r="I92" t="n">
         <v>0</v>
       </c>
-      <c r="J92"/>
-      <c r="K92"/>
-      <c r="L92"/>
+      <c r="J92" t="n">
+        <v>1</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0.1115625</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0.230688164317543</v>
+      </c>
       <c r="M92" t="b">
         <v>0</v>
       </c>
@@ -6510,9 +7056,15 @@
       <c r="I93" t="n">
         <v>0</v>
       </c>
-      <c r="J93"/>
-      <c r="K93"/>
-      <c r="L93"/>
+      <c r="J93" t="n">
+        <v>1</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0.107708333333333</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0.236442387153339</v>
+      </c>
       <c r="M93" t="b">
         <v>0</v>
       </c>
@@ -6563,9 +7115,15 @@
       <c r="I94" t="n">
         <v>0.104166666666667</v>
       </c>
-      <c r="J94"/>
-      <c r="K94"/>
-      <c r="L94"/>
+      <c r="J94" t="n">
+        <v>0.442786069651741</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0.177395833333333</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0.25204164851161</v>
+      </c>
       <c r="M94" t="b">
         <v>0</v>
       </c>
@@ -6616,9 +7174,15 @@
       <c r="I95" t="n">
         <v>0.25</v>
       </c>
-      <c r="J95"/>
-      <c r="K95"/>
-      <c r="L95"/>
+      <c r="J95" t="n">
+        <v>0.492537313432836</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0.297083333333333</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0.229240318604571</v>
+      </c>
       <c r="M95" t="b">
         <v>0</v>
       </c>
@@ -6669,9 +7233,15 @@
       <c r="I96" t="n">
         <v>0</v>
       </c>
-      <c r="J96"/>
-      <c r="K96"/>
-      <c r="L96"/>
+      <c r="J96" t="n">
+        <v>1</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0.0257291666666667</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0.125017054601498</v>
+      </c>
       <c r="M96" t="b">
         <v>0</v>
       </c>
@@ -6722,9 +7292,15 @@
       <c r="I97" t="n">
         <v>0.25</v>
       </c>
-      <c r="J97"/>
-      <c r="K97"/>
-      <c r="L97"/>
+      <c r="J97" t="n">
+        <v>0.716417910447761</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0.4228125</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.257823542455937</v>
+      </c>
       <c r="M97" t="b">
         <v>0</v>
       </c>
@@ -6770,14 +7346,20 @@
         <v>23</v>
       </c>
       <c r="H98" t="n">
-        <v>0.0833333333333333</v>
+        <v>0.125</v>
       </c>
       <c r="I98" t="n">
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="J98"/>
-      <c r="K98"/>
-      <c r="L98"/>
+        <v>0.125</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0.776119402985075</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0.351979166666667</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0.265225882122388</v>
+      </c>
       <c r="M98" t="b">
         <v>0</v>
       </c>
@@ -6828,9 +7410,15 @@
       <c r="I99" t="n">
         <v>0</v>
       </c>
-      <c r="J99"/>
-      <c r="K99"/>
-      <c r="L99"/>
+      <c r="J99" t="n">
+        <v>1</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0.0934375</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0.215607690033392</v>
+      </c>
       <c r="M99" t="b">
         <v>0</v>
       </c>
@@ -6881,9 +7469,15 @@
       <c r="I100" t="n">
         <v>0.125</v>
       </c>
-      <c r="J100"/>
-      <c r="K100"/>
-      <c r="L100"/>
+      <c r="J100" t="n">
+        <v>0.233830845771144</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0.0927083333333333</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0.211726451118641</v>
+      </c>
       <c r="M100" t="b">
         <v>0</v>
       </c>
@@ -6934,9 +7528,15 @@
       <c r="I101" t="n">
         <v>0.4375</v>
       </c>
-      <c r="J101"/>
-      <c r="K101"/>
-      <c r="L101"/>
+      <c r="J101" t="n">
+        <v>0.199004975124378</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0.197395833333333</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0.263224498552189</v>
+      </c>
       <c r="M101" t="b">
         <v>0</v>
       </c>
@@ -6987,9 +7587,15 @@
       <c r="I102" t="n">
         <v>0.333333333333333</v>
       </c>
-      <c r="J102"/>
-      <c r="K102"/>
-      <c r="L102"/>
+      <c r="J102" t="n">
+        <v>0.393034825870647</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0.298020833333333</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0.213485266993297</v>
+      </c>
       <c r="M102" t="b">
         <v>0</v>
       </c>
@@ -7040,9 +7646,15 @@
       <c r="I103" t="n">
         <v>0</v>
       </c>
-      <c r="J103"/>
-      <c r="K103"/>
-      <c r="L103"/>
+      <c r="J103" t="n">
+        <v>1</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0.0167708333333333</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0.0926930108448954</v>
+      </c>
       <c r="M103" t="b">
         <v>0</v>
       </c>
@@ -7093,9 +7705,15 @@
       <c r="I104" t="n">
         <v>0.729166666666667</v>
       </c>
-      <c r="J104"/>
-      <c r="K104"/>
-      <c r="L104"/>
+      <c r="J104" t="n">
+        <v>0.134328358208955</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0.441979166666667</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0.241947700012745</v>
+      </c>
       <c r="M104" t="b">
         <v>0</v>
       </c>
@@ -7146,9 +7764,15 @@
       <c r="I105" t="n">
         <v>0</v>
       </c>
-      <c r="J105"/>
-      <c r="K105"/>
-      <c r="L105"/>
+      <c r="J105" t="n">
+        <v>1</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0.314895833333333</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0.265404926158137</v>
+      </c>
       <c r="M105" t="b">
         <v>0</v>
       </c>
@@ -7199,9 +7823,15 @@
       <c r="I106" t="n">
         <v>0</v>
       </c>
-      <c r="J106"/>
-      <c r="K106"/>
-      <c r="L106"/>
+      <c r="J106" t="n">
+        <v>1</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0.104196428571429</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0.207776661588622</v>
+      </c>
       <c r="M106" t="b">
         <v>0</v>
       </c>
@@ -7252,9 +7882,15 @@
       <c r="I107" t="n">
         <v>0</v>
       </c>
-      <c r="J107"/>
-      <c r="K107"/>
-      <c r="L107"/>
+      <c r="J107" t="n">
+        <v>1</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0.113214285714286</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0.213674949161307</v>
+      </c>
       <c r="M107" t="b">
         <v>0</v>
       </c>
@@ -7305,9 +7941,15 @@
       <c r="I108" t="n">
         <v>0.285714285714286</v>
       </c>
-      <c r="J108"/>
-      <c r="K108"/>
-      <c r="L108"/>
+      <c r="J108" t="n">
+        <v>0.373134328358209</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0.246339285714286</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0.237256934949697</v>
+      </c>
       <c r="M108" t="b">
         <v>0</v>
       </c>
@@ -7358,9 +8000,15 @@
       <c r="I109" t="n">
         <v>0.428571428571428</v>
       </c>
-      <c r="J109"/>
-      <c r="K109"/>
-      <c r="L109"/>
+      <c r="J109" t="n">
+        <v>0.243781094527363</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0.276964285714286</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0.19340731063323</v>
+      </c>
       <c r="M109" t="b">
         <v>0</v>
       </c>
@@ -7411,9 +8059,15 @@
       <c r="I110" t="n">
         <v>0</v>
       </c>
-      <c r="J110"/>
-      <c r="K110"/>
-      <c r="L110"/>
+      <c r="J110" t="n">
+        <v>1</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0.00205357142857143</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0.0266238528978017</v>
+      </c>
       <c r="M110" t="b">
         <v>0</v>
       </c>
@@ -7464,9 +8118,15 @@
       <c r="I111" t="n">
         <v>0.410714285714286</v>
       </c>
-      <c r="J111"/>
-      <c r="K111"/>
-      <c r="L111"/>
+      <c r="J111" t="n">
+        <v>0.552238805970149</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0.434821428571429</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0.237035321776882</v>
+      </c>
       <c r="M111" t="b">
         <v>0</v>
       </c>
@@ -7512,14 +8172,20 @@
         <v>23</v>
       </c>
       <c r="H112" t="n">
-        <v>0.178571428571429</v>
+        <v>0.375</v>
       </c>
       <c r="I112" t="n">
-        <v>0.178571428571429</v>
-      </c>
-      <c r="J112"/>
-      <c r="K112"/>
-      <c r="L112"/>
+        <v>0.375</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0.398009950248756</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0.234814340130321</v>
+      </c>
       <c r="M112" t="b">
         <v>0</v>
       </c>
@@ -7570,9 +8236,15 @@
       <c r="I113" t="n">
         <v>0</v>
       </c>
-      <c r="J113"/>
-      <c r="K113"/>
-      <c r="L113"/>
+      <c r="J113" t="n">
+        <v>1</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0.1025</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0.233874073703196</v>
+      </c>
       <c r="M113" t="b">
         <v>0</v>
       </c>
@@ -7623,9 +8295,15 @@
       <c r="I114" t="n">
         <v>0</v>
       </c>
-      <c r="J114"/>
-      <c r="K114"/>
-      <c r="L114"/>
+      <c r="J114" t="n">
+        <v>1</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0.105625</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0.235543575607896</v>
+      </c>
       <c r="M114" t="b">
         <v>0</v>
       </c>
@@ -7676,9 +8354,15 @@
       <c r="I115" t="n">
         <v>0</v>
       </c>
-      <c r="J115"/>
-      <c r="K115"/>
-      <c r="L115"/>
+      <c r="J115" t="n">
+        <v>1</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0.306919642857143</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0.253280126088554</v>
+      </c>
       <c r="M115" t="b">
         <v>0</v>
       </c>
@@ -7729,9 +8413,15 @@
       <c r="I116" t="n">
         <v>0</v>
       </c>
-      <c r="J116"/>
-      <c r="K116"/>
-      <c r="L116"/>
+      <c r="J116" t="n">
+        <v>1</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0.344821428571429</v>
+      </c>
+      <c r="L116" t="n">
+        <v>0.223648285907024</v>
+      </c>
       <c r="M116" t="b">
         <v>0</v>
       </c>
@@ -7782,9 +8472,15 @@
       <c r="I117" t="n">
         <v>0</v>
       </c>
-      <c r="J117"/>
-      <c r="K117"/>
-      <c r="L117"/>
+      <c r="J117" t="n">
+        <v>1</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.035625</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.142402109792109</v>
+      </c>
       <c r="M117" t="b">
         <v>0</v>
       </c>
@@ -7835,9 +8531,15 @@
       <c r="I118" t="n">
         <v>0</v>
       </c>
-      <c r="J118"/>
-      <c r="K118"/>
-      <c r="L118"/>
+      <c r="J118" t="n">
+        <v>1</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.456964285714286</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.244190721676662</v>
+      </c>
       <c r="M118" t="b">
         <v>0</v>
       </c>
@@ -7883,14 +8585,20 @@
         <v>23</v>
       </c>
       <c r="H119" t="n">
-        <v>0.357142857142857</v>
+        <v>0.571428571428571</v>
       </c>
       <c r="I119" t="n">
-        <v>0.357142857142857</v>
-      </c>
-      <c r="J119"/>
-      <c r="K119"/>
-      <c r="L119"/>
+        <v>0.571428571428571</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.199004975124378</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.332767857142857</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.255215426742345</v>
+      </c>
       <c r="M119" t="b">
         <v>0</v>
       </c>
@@ -7941,9 +8649,15 @@
       <c r="I120" t="n">
         <v>0</v>
       </c>
-      <c r="J120"/>
-      <c r="K120"/>
-      <c r="L120"/>
+      <c r="J120" t="n">
+        <v>1</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.0926785714285714</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.205048810320581</v>
+      </c>
       <c r="M120" t="b">
         <v>0</v>
       </c>
@@ -7994,9 +8708,15 @@
       <c r="I121" t="n">
         <v>0</v>
       </c>
-      <c r="J121"/>
-      <c r="K121"/>
-      <c r="L121"/>
+      <c r="J121" t="n">
+        <v>1</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.0825</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.188910659324561</v>
+      </c>
       <c r="M121" t="b">
         <v>0</v>
       </c>
@@ -8047,9 +8767,15 @@
       <c r="I122" t="n">
         <v>0.107142857142857</v>
       </c>
-      <c r="J122"/>
-      <c r="K122"/>
-      <c r="L122"/>
+      <c r="J122" t="n">
+        <v>0.736318407960199</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.261428571428571</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.241543998539475</v>
+      </c>
       <c r="M122" t="b">
         <v>0</v>
       </c>
@@ -8100,9 +8826,15 @@
       <c r="I123" t="n">
         <v>0.303571428571429</v>
       </c>
-      <c r="J123"/>
-      <c r="K123"/>
-      <c r="L123"/>
+      <c r="J123" t="n">
+        <v>0.427860696517413</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.289285714285714</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.211690130891281</v>
+      </c>
       <c r="M123" t="b">
         <v>0</v>
       </c>
@@ -8153,9 +8885,15 @@
       <c r="I124" t="n">
         <v>0</v>
       </c>
-      <c r="J124"/>
-      <c r="K124"/>
-      <c r="L124"/>
+      <c r="J124" t="n">
+        <v>1</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.0246428571428571</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.127990331555934</v>
+      </c>
       <c r="M124" t="b">
         <v>0</v>
       </c>
@@ -8206,9 +8944,15 @@
       <c r="I125" t="n">
         <v>0.535714285714286</v>
       </c>
-      <c r="J125"/>
-      <c r="K125"/>
-      <c r="L125"/>
+      <c r="J125" t="n">
+        <v>0.353233830845771</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.428035714285714</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.237414669534603</v>
+      </c>
       <c r="M125" t="b">
         <v>0</v>
       </c>
@@ -8254,14 +8998,20 @@
         <v>23</v>
       </c>
       <c r="H126" t="n">
-        <v>0.196428571428571</v>
+        <v>0.303571428571429</v>
       </c>
       <c r="I126" t="n">
-        <v>0.196428571428571</v>
-      </c>
-      <c r="J126"/>
-      <c r="K126"/>
-      <c r="L126"/>
+        <v>0.303571428571429</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.527363184079602</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.351696428571429</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.267795503197241</v>
+      </c>
       <c r="M126" t="b">
         <v>0</v>
       </c>
@@ -8312,9 +9062,15 @@
       <c r="I127" t="n">
         <v>0</v>
       </c>
-      <c r="J127"/>
-      <c r="K127"/>
-      <c r="L127"/>
+      <c r="J127" t="n">
+        <v>1</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.0916964285714286</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.201487882058065</v>
+      </c>
       <c r="M127" t="b">
         <v>0</v>
       </c>
@@ -8365,9 +9121,15 @@
       <c r="I128" t="n">
         <v>0</v>
       </c>
-      <c r="J128"/>
-      <c r="K128"/>
-      <c r="L128"/>
+      <c r="J128" t="n">
+        <v>1</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.0959821428571429</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.210113101254876</v>
+      </c>
       <c r="M128" t="b">
         <v>0</v>
       </c>
@@ -8418,9 +9180,15 @@
       <c r="I129" t="n">
         <v>0.482142857142857</v>
       </c>
-      <c r="J129"/>
-      <c r="K129"/>
-      <c r="L129"/>
+      <c r="J129" t="n">
+        <v>0.218905472636816</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.25125</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.24394333708367</v>
+      </c>
       <c r="M129" t="b">
         <v>0</v>
       </c>
@@ -8471,9 +9239,15 @@
       <c r="I130" t="n">
         <v>0.357142857142857</v>
       </c>
-      <c r="J130"/>
-      <c r="K130"/>
-      <c r="L130"/>
+      <c r="J130" t="n">
+        <v>0.358208955223881</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.277678571428571</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.215841074043334</v>
+      </c>
       <c r="M130" t="b">
         <v>0</v>
       </c>
@@ -8524,9 +9298,15 @@
       <c r="I131" t="n">
         <v>0</v>
       </c>
-      <c r="J131"/>
-      <c r="K131"/>
-      <c r="L131"/>
+      <c r="J131" t="n">
+        <v>1</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.0140178571428572</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.10120349123823</v>
+      </c>
       <c r="M131" t="b">
         <v>0</v>
       </c>
@@ -8577,9 +9357,15 @@
       <c r="I132" t="n">
         <v>0.464285714285714</v>
       </c>
-      <c r="J132"/>
-      <c r="K132"/>
-      <c r="L132"/>
+      <c r="J132" t="n">
+        <v>0.383084577114428</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.401696428571429</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.238975980416396</v>
+      </c>
       <c r="M132" t="b">
         <v>0</v>
       </c>
@@ -8625,14 +9411,20 @@
         <v>23</v>
       </c>
       <c r="H133" t="n">
-        <v>0.142857142857143</v>
+        <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>0.142857142857143</v>
-      </c>
-      <c r="J133"/>
-      <c r="K133"/>
-      <c r="L133"/>
+        <v>0</v>
+      </c>
+      <c r="J133" t="n">
+        <v>1</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.330178571428571</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.249897361250336</v>
+      </c>
       <c r="M133" t="b">
         <v>0</v>
       </c>
@@ -8683,9 +9475,15 @@
       <c r="I134" t="n">
         <v>0</v>
       </c>
-      <c r="J134"/>
-      <c r="K134"/>
-      <c r="L134"/>
+      <c r="J134" t="n">
+        <v>1</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.0917708333333333</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.203386597107985</v>
+      </c>
       <c r="M134" t="b">
         <v>0</v>
       </c>
@@ -8736,9 +9534,15 @@
       <c r="I135" t="n">
         <v>0</v>
       </c>
-      <c r="J135"/>
-      <c r="K135"/>
-      <c r="L135"/>
+      <c r="J135" t="n">
+        <v>1</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.104479166666667</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.224162836104277</v>
+      </c>
       <c r="M135" t="b">
         <v>0</v>
       </c>
@@ -8789,9 +9593,15 @@
       <c r="I136" t="n">
         <v>0</v>
       </c>
-      <c r="J136"/>
-      <c r="K136"/>
-      <c r="L136"/>
+      <c r="J136" t="n">
+        <v>1</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.180572916666667</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.252435869807093</v>
+      </c>
       <c r="M136" t="b">
         <v>0</v>
       </c>
@@ -8842,9 +9652,15 @@
       <c r="I137" t="n">
         <v>0.0416666666666667</v>
       </c>
-      <c r="J137"/>
-      <c r="K137"/>
-      <c r="L137"/>
+      <c r="J137" t="n">
+        <v>0.890547263681592</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.274895833333333</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.198882116936255</v>
+      </c>
       <c r="M137" t="b">
         <v>0</v>
       </c>
@@ -8895,9 +9711,15 @@
       <c r="I138" t="n">
         <v>0</v>
       </c>
-      <c r="J138"/>
-      <c r="K138"/>
-      <c r="L138"/>
+      <c r="J138" t="n">
+        <v>1</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.0189583333333333</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.0872006224877765</v>
+      </c>
       <c r="M138" t="b">
         <v>0</v>
       </c>
@@ -8948,9 +9770,15 @@
       <c r="I139" t="n">
         <v>0.229166666666667</v>
       </c>
-      <c r="J139"/>
-      <c r="K139"/>
-      <c r="L139"/>
+      <c r="J139" t="n">
+        <v>0.711442786069652</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.420729166666667</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.256125213893384</v>
+      </c>
       <c r="M139" t="b">
         <v>0</v>
       </c>
@@ -8996,14 +9824,20 @@
         <v>23</v>
       </c>
       <c r="H140" t="n">
-        <v>0.333333333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="I140" t="n">
-        <v>0.333333333333333</v>
-      </c>
-      <c r="J140"/>
-      <c r="K140"/>
-      <c r="L140"/>
+        <v>0.4375</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.36318407960199</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.340208333333333</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.265601525796266</v>
+      </c>
       <c r="M140" t="b">
         <v>0</v>
       </c>
@@ -9054,9 +9888,15 @@
       <c r="I141" t="n">
         <v>0</v>
       </c>
-      <c r="J141"/>
-      <c r="K141"/>
-      <c r="L141"/>
+      <c r="J141" t="n">
+        <v>1</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.0548958333333333</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.163378064873891</v>
+      </c>
       <c r="M141" t="b">
         <v>0</v>
       </c>
@@ -9107,9 +9947,15 @@
       <c r="I142" t="n">
         <v>0</v>
       </c>
-      <c r="J142"/>
-      <c r="K142"/>
-      <c r="L142"/>
+      <c r="J142" t="n">
+        <v>1</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.0726041666666667</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.192510268195109</v>
+      </c>
       <c r="M142" t="b">
         <v>0</v>
       </c>
@@ -9160,9 +10006,15 @@
       <c r="I143" t="n">
         <v>0</v>
       </c>
-      <c r="J143"/>
-      <c r="K143"/>
-      <c r="L143"/>
+      <c r="J143" t="n">
+        <v>1</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.181041666666667</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.245700305403508</v>
+      </c>
       <c r="M143" t="b">
         <v>0</v>
       </c>
@@ -9213,9 +10065,15 @@
       <c r="I144" t="n">
         <v>0.1875</v>
       </c>
-      <c r="J144"/>
-      <c r="K144"/>
-      <c r="L144"/>
+      <c r="J144" t="n">
+        <v>0.532338308457711</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0.262604166666667</v>
+      </c>
+      <c r="L144" t="n">
+        <v>0.215809102678398</v>
+      </c>
       <c r="M144" t="b">
         <v>0</v>
       </c>
@@ -9266,9 +10124,15 @@
       <c r="I145" t="n">
         <v>0</v>
       </c>
-      <c r="J145"/>
-      <c r="K145"/>
-      <c r="L145"/>
+      <c r="J145" t="n">
+        <v>1</v>
+      </c>
+      <c r="K145" t="n">
+        <v>0.0157291666666667</v>
+      </c>
+      <c r="L145" t="n">
+        <v>0.115919807854461</v>
+      </c>
       <c r="M145" t="b">
         <v>0</v>
       </c>
@@ -9319,9 +10183,15 @@
       <c r="I146" t="n">
         <v>0.166666666666667</v>
       </c>
-      <c r="J146"/>
-      <c r="K146"/>
-      <c r="L146"/>
+      <c r="J146" t="n">
+        <v>0.840796019900497</v>
+      </c>
+      <c r="K146" t="n">
+        <v>0.415104166666667</v>
+      </c>
+      <c r="L146" t="n">
+        <v>0.244637645779246</v>
+      </c>
       <c r="M146" t="b">
         <v>0</v>
       </c>
@@ -9367,14 +10237,20 @@
         <v>23</v>
       </c>
       <c r="H147" t="n">
-        <v>0.541666666666667</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="I147" t="n">
-        <v>0.541666666666667</v>
-      </c>
-      <c r="J147"/>
-      <c r="K147"/>
-      <c r="L147"/>
+        <v>0.583333333333333</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0.18407960199005</v>
+      </c>
+      <c r="K147" t="n">
+        <v>0.320833333333333</v>
+      </c>
+      <c r="L147" t="n">
+        <v>0.269594350650839</v>
+      </c>
       <c r="M147" t="b">
         <v>0</v>
       </c>
@@ -9425,9 +10301,15 @@
       <c r="I148" t="n">
         <v>0</v>
       </c>
-      <c r="J148"/>
-      <c r="K148"/>
-      <c r="L148"/>
+      <c r="J148" t="n">
+        <v>1</v>
+      </c>
+      <c r="K148" t="n">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="L148" t="n">
+        <v>0.137226582121946</v>
+      </c>
       <c r="M148" t="b">
         <v>0</v>
       </c>
@@ -9478,9 +10360,15 @@
       <c r="I149" t="n">
         <v>0</v>
       </c>
-      <c r="J149"/>
-      <c r="K149"/>
-      <c r="L149"/>
+      <c r="J149" t="n">
+        <v>1</v>
+      </c>
+      <c r="K149" t="n">
+        <v>0.0594791666666667</v>
+      </c>
+      <c r="L149" t="n">
+        <v>0.162537811550287</v>
+      </c>
       <c r="M149" t="b">
         <v>0</v>
       </c>
@@ -9531,9 +10419,15 @@
       <c r="I150" t="n">
         <v>0.125</v>
       </c>
-      <c r="J150"/>
-      <c r="K150"/>
-      <c r="L150"/>
+      <c r="J150" t="n">
+        <v>0.437810945273632</v>
+      </c>
+      <c r="K150" t="n">
+        <v>0.1609375</v>
+      </c>
+      <c r="L150" t="n">
+        <v>0.230934228587746</v>
+      </c>
       <c r="M150" t="b">
         <v>0</v>
       </c>
@@ -9584,9 +10478,15 @@
       <c r="I151" t="n">
         <v>0.229166666666667</v>
       </c>
-      <c r="J151"/>
-      <c r="K151"/>
-      <c r="L151"/>
+      <c r="J151" t="n">
+        <v>0.447761194029851</v>
+      </c>
+      <c r="K151" t="n">
+        <v>0.229791666666667</v>
+      </c>
+      <c r="L151" t="n">
+        <v>0.192611442322537</v>
+      </c>
       <c r="M151" t="b">
         <v>0</v>
       </c>
@@ -9637,9 +10537,15 @@
       <c r="I152" t="n">
         <v>0</v>
       </c>
-      <c r="J152"/>
-      <c r="K152"/>
-      <c r="L152"/>
+      <c r="J152" t="n">
+        <v>1</v>
+      </c>
+      <c r="K152" t="n">
+        <v>0.00843750000000001</v>
+      </c>
+      <c r="L152" t="n">
+        <v>0.0739922024154292</v>
+      </c>
       <c r="M152" t="b">
         <v>0</v>
       </c>
@@ -9690,9 +10596,15 @@
       <c r="I153" t="n">
         <v>0.270833333333333</v>
       </c>
-      <c r="J153"/>
-      <c r="K153"/>
-      <c r="L153"/>
+      <c r="J153" t="n">
+        <v>0.656716417910448</v>
+      </c>
+      <c r="K153" t="n">
+        <v>0.4046875</v>
+      </c>
+      <c r="L153" t="n">
+        <v>0.249995092602589</v>
+      </c>
       <c r="M153" t="b">
         <v>0</v>
       </c>
@@ -9738,14 +10650,20 @@
         <v>23</v>
       </c>
       <c r="H154" t="n">
-        <v>0.229166666666667</v>
+        <v>0.270833333333333</v>
       </c>
       <c r="I154" t="n">
-        <v>0.229166666666667</v>
-      </c>
-      <c r="J154"/>
-      <c r="K154"/>
-      <c r="L154"/>
+        <v>0.270833333333333</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0.567164179104478</v>
+      </c>
+      <c r="K154" t="n">
+        <v>0.3546875</v>
+      </c>
+      <c r="L154" t="n">
+        <v>0.254517029811066</v>
+      </c>
       <c r="M154" t="b">
         <v>0</v>
       </c>
